--- a/outputs/prediction_module_seed/db_init_data.xlsx
+++ b/outputs/prediction_module_seed/db_init_data.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="1" r:id="R0ef3e4eba8f4401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataSources" sheetId="2" r:id="R9f9e70a1b6aa4c52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserTypes" sheetId="3" r:id="R7b27192156a54c0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductTypes" sheetId="4" r:id="R8e003c8b71d64f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="5" r:id="R789fb37c8d5e4e74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MeasurementTypes" sheetId="6" r:id="R67ae668b3f924db0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SensorTypes" sheetId="7" r:id="R6bfc3cc9657b4665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="8" r:id="Rd227e1844c9b4965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcessConfigurations" sheetId="9" r:id="R291a78849fd548d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcessSteps" sheetId="10" r:id="R3e25ea1678d14ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssetProcessSteps" sheetId="11" r:id="R74d3e79694b745bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routing" sheetId="12" r:id="Rf33491333d5f440a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FailureTypes" sheetId="13" r:id="R9024312df74645d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssetFailureTypes" sheetId="14" r:id="R894e0ea01395479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SensorFailureTypes" sheetId="15" r:id="R29ae7c2ca5b7497b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SensorStatistics" sheetId="16" r:id="R4e73b02a47894c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measurements" sheetId="17" r:id="R34f8a067e7b841e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EtaBetas" sheetId="18" r:id="R200c0a07be664f9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gammas" sheetId="19" r:id="Ra3c92b410bf24ecc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssetWorksheetLists" sheetId="20" r:id="Re30f805b294c40e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OperationsDoneLists" sheetId="21" r:id="R64879dbd88f1416f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="1" r:id="R482fb45829de4ce3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataSources" sheetId="2" r:id="Rb4ed87190fb04faa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UserTypes" sheetId="3" r:id="R43d4df43e0844276"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductTypes" sheetId="4" r:id="Rc83434442e244475"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="5" r:id="R5f022e0fe1114bc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MeasurementTypes" sheetId="6" r:id="Rbacc898a1aa34992"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SensorTypes" sheetId="7" r:id="R5e1e96f411f0437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensors" sheetId="8" r:id="R6bfe5f8b511c4a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcessConfigurations" sheetId="9" r:id="R77c83382c02240f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProcessSteps" sheetId="10" r:id="R0bf704af0b574cfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssetProcessSteps" sheetId="11" r:id="R519da7b6d81c49aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routing" sheetId="12" r:id="R54c595c8febd4b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FailureTypes" sheetId="13" r:id="R22d59d7608a54b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssetFailureTypes" sheetId="14" r:id="R4c5c1604c1ad4ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SensorFailureTypes" sheetId="15" r:id="R1fdeef49b55843ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SensorStatistics" sheetId="16" r:id="R05e513fee2d04ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measurements" sheetId="17" r:id="R14a7ba8152544c4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EtaBetas" sheetId="18" r:id="R2b7c2dbb4d714d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gammas" sheetId="19" r:id="R58c7bf371e5842f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssetWorksheetLists" sheetId="20" r:id="R310eff81984348ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OperationsDoneLists" sheetId="21" r:id="Rb6e1fceb918d4f49"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -599,7 +599,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -609,6 +609,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -643,7 +648,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general"/>
@@ -770,6 +775,16 @@
     <x:xf numFmtId="204" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="204" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -881,7 +896,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="SensorStatisticsTable" displayName="SensorStatisticsTable" ref="A4:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="SensorStatisticsTable" displayName="SensorStatisticsTable" ref="A4:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="sensor_statistic_key"/>
     <x:tableColumn id="2" name="sensor_key"/>
@@ -1458,7 +1473,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa21dfc16721424a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac9c710609f4c5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1613,7 +1628,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R655a6fa0a58e48a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc60eada9227a4ee9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1768,7 +1783,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda5563890dca4bea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R493bd744d51d4d1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1934,7 +1949,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5c1b78b034941ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf31944879b524045"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2026,7 +2041,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R098f95274ae846fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31298f6a71ea459e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2167,7 +2182,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59abf497f6cf4043"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5acd09d49da14f9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2761,7 +2776,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f692e2a8995404f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7368b213861465f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2770,10 +2785,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="21" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -2783,128 +2798,98 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="33" t="str">
+      <x:c r="A4" s="46" t="str">
         <x:v>sensor_statistic_key</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="str">
+      <x:c r="B4" s="46" t="str">
         <x:v>sensor_key</x:v>
       </x:c>
-      <x:c r="C4" s="33" t="str">
+      <x:c r="C4" s="46" t="str">
         <x:v>standard_deviation_value</x:v>
       </x:c>
-      <x:c r="D4" s="33" t="str">
+      <x:c r="D4" s="46" t="str">
         <x:v>average_value</x:v>
       </x:c>
-      <x:c r="E4" s="33" t="str">
+      <x:c r="E4" s="46" t="str">
         <x:v>learning_time</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="34" t="str">
+      <x:c r="A5" s="28" t="str">
         <x:v>sensor_stat_1</x:v>
       </x:c>
-      <x:c r="B5" s="34" t="str">
-        <x:v>tray_in_vqc</x:v>
-      </x:c>
-      <x:c r="C5" s="39" t="n">
-        <x:v>0.45</x:v>
-      </x:c>
-      <x:c r="D5" s="39" t="n">
-        <x:v>26.4</x:v>
-      </x:c>
-      <x:c r="E5" s="38" t="n">
-        <x:v>45992</x:v>
+      <x:c r="B5" s="28" t="str">
+        <x:v>tray_in_vqc</x:v>
+      </x:c>
+      <x:c r="C5" s="41" t="n">
+        <x:v>11.529079565464569</x:v>
+      </x:c>
+      <x:c r="D5" s="41" t="n">
+        <x:v>29.192629563265918</x:v>
+      </x:c>
+      <x:c r="E5" s="42" t="n">
+        <x:v>46033</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="34" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>sensor_stat_2</x:v>
       </x:c>
-      <x:c r="B6" s="34" t="str">
-        <x:v>tray_out_vqc</x:v>
-      </x:c>
-      <x:c r="C6" s="39" t="n">
-        <x:v>1.1</x:v>
-      </x:c>
-      <x:c r="D6" s="39" t="n">
-        <x:v>104.5</x:v>
-      </x:c>
-      <x:c r="E6" s="38" t="n">
-        <x:v>45992</x:v>
+      <x:c r="B6" s="28" t="str">
+        <x:v>tray_out_vqc</x:v>
+      </x:c>
+      <x:c r="C6" s="41" t="n">
+        <x:v>5.866151139048425</x:v>
+      </x:c>
+      <x:c r="D6" s="41" t="n">
+        <x:v>109.8444798173757</x:v>
+      </x:c>
+      <x:c r="E6" s="42" t="n">
+        <x:v>46033</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="28" t="str">
         <x:v>sensor_stat_3</x:v>
       </x:c>
-      <x:c r="B7" s="34" t="str">
+      <x:c r="B7" s="28" t="str">
         <x:v>cylinder_status_vqc</x:v>
       </x:c>
-      <x:c r="C7" s="39" t="n">
-        <x:v>0.35</x:v>
-      </x:c>
-      <x:c r="D7" s="39" t="n">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="E7" s="38" t="n">
-        <x:v>45992</x:v>
+      <x:c r="C7" s="41" t="n">
+        <x:v>2.8829210693675886</x:v>
+      </x:c>
+      <x:c r="D7" s="41" t="n">
+        <x:v>0.10196266102731127</x:v>
+      </x:c>
+      <x:c r="E7" s="42" t="n">
+        <x:v>46033</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="34" t="str">
-        <x:v>sensor_stat_4</x:v>
-      </x:c>
-      <x:c r="B8" s="34" t="str">
-        <x:v>tray_in_vqc</x:v>
-      </x:c>
-      <x:c r="C8" s="39" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="D8" s="39" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E8" s="38" t="n">
-        <x:v>46023</x:v>
-      </x:c>
+      <x:c r="A8"/>
+      <x:c r="B8"/>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="34" t="str">
-        <x:v>sensor_stat_5</x:v>
-      </x:c>
-      <x:c r="B9" s="34" t="str">
-        <x:v>tray_out_vqc</x:v>
-      </x:c>
-      <x:c r="C9" s="39" t="n">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="D9" s="39" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="E9" s="38" t="n">
-        <x:v>46023</x:v>
-      </x:c>
+      <x:c r="A9"/>
+      <x:c r="B9"/>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="34" t="str">
-        <x:v>sensor_stat_6</x:v>
-      </x:c>
-      <x:c r="B10" s="34" t="str">
-        <x:v>cylinder_status_vqc</x:v>
-      </x:c>
-      <x:c r="C10" s="39" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="D10" s="39" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E10" s="38" t="n">
-        <x:v>46023</x:v>
-      </x:c>
+      <x:c r="A10"/>
+      <x:c r="B10"/>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a421b4abc1748a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d58d079bec14556"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51905,7 +51890,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8023d149e9b447b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R731a5f43bcc74464"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52014,7 +51999,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R165e6a0ec9e24009"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcd31f1998de44ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52922,7 +52907,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7120c790d51f44c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R442b0288a3c64f30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52988,7 +52973,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd98ceaf059d4df5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88298fb7a5b24f76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53189,7 +53174,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1735e23611bb4390"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18b21a9c2ab24248"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53604,7 +53589,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9e1949612264f11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68346f0f2bc74451"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53690,7 +53675,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9cd37de3f39483d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7523e6f988904a62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53779,7 +53764,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ba1db084ad5464c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0c510b057514557"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53901,7 +53886,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb3bdb8725b04739"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R700a9d3701954b39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54025,7 +54010,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red272f975a5d4467"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad61af5a0b0c4cb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54181,7 +54166,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cd8779eb4394100"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd61d4cd5d1d74a63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54635,7 +54620,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd32de329421c4c00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R192ea96fd41b4711"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54707,7 +54692,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R123bd97a9d3d4500"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf438a4aaafab4af3"/>
   </x:tableParts>
 </x:worksheet>
 </file>